--- a/design/亲密度与事件.xlsx
+++ b/design/亲密度与事件.xlsx
@@ -18,7 +18,7 @@
     <definedName name="列表_触发时机">'下拉选项'!$A$2:$A$14</definedName>
     <definedName name="列表_亲密度行为">'下拉选项'!$B$2:$B$9</definedName>
     <definedName name="列表_次数">'下拉选项'!$C$2:$C$4</definedName>
-    <definedName name="列表_动作">'下拉选项'!$D$2:$D$17</definedName>
+    <definedName name="列表_动作">'下拉选项'!$D$2:$D$19</definedName>
     <definedName name="列表_台词场合">'下拉选项'!$E$2:$E$12</definedName>
     <definedName name="列表_是否">'下拉选项'!$F$2:$F$3</definedName>
   </definedNames>
@@ -869,6 +869,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
@@ -4088,7 +4089,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>到点提醒（待做）</t>
+          <t>到点提醒</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
@@ -4100,21 +4101,28 @@
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>看你的屏幕（待做）</t>
+          <t>看屏幕</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>敲键盘写代码（待做）</t>
+          <t>敲键盘</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>吐泡泡（待做）</t>
+          <t>吐泡泡</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>余额充足</t>
         </is>
       </c>
     </row>
@@ -4122,6 +4130,11 @@
       <c r="A19" s="12" t="inlineStr">
         <is>
           <t>这些选项由程序定义，别改。要加新选项先跟 Claude 说。</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>余额见底</t>
         </is>
       </c>
     </row>
